--- a/data/trans_dic/P25A$medico-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,63</t>
+          <t>0,0; 36,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,14</t>
+          <t>0,0; 31,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 51,12</t>
+          <t>5,87; 51,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,52</t>
+          <t>0,0; 21,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,41</t>
+          <t>0,0; 17,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 33,68</t>
+          <t>3,64; 33,1</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 25,82</t>
+          <t>3,87; 26,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,26</t>
+          <t>1,34; 13,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 16,79</t>
+          <t>2,11; 17,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 17,34</t>
+          <t>2,86; 17,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 13,83</t>
+          <t>2,48; 14,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,8</t>
+          <t>0,0; 10,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 16,67</t>
+          <t>4,31; 16,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,34</t>
+          <t>3,26; 11,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,5</t>
+          <t>1,8; 10,55</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 15,51</t>
+          <t>2,52; 15,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,97</t>
+          <t>2,62; 12,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,9</t>
+          <t>1,21; 11,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,52</t>
+          <t>0,0; 14,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,43</t>
+          <t>0,77; 6,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,82</t>
+          <t>1,04; 9,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 10,61</t>
+          <t>2,43; 10,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,92</t>
+          <t>2,15; 7,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,67</t>
+          <t>1,73; 7,7</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 24,23</t>
+          <t>10,71; 24,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 14,76</t>
+          <t>5,22; 14,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,15; 28,56</t>
+          <t>13,48; 30,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,57</t>
+          <t>0,0; 10,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 17,51</t>
+          <t>4,59; 16,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 17,22</t>
+          <t>4,44; 16,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 18,44</t>
+          <t>7,94; 17,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 13,35</t>
+          <t>5,91; 13,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 20,75</t>
+          <t>10,51; 21,42</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,13; 41,93</t>
+          <t>25,49; 41,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,66</t>
+          <t>13,44; 27,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,74; 29,44</t>
+          <t>14,78; 29,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,34</t>
+          <t>0,0; 28,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 30,67</t>
+          <t>8,14; 32,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 26,85</t>
+          <t>6,06; 26,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,87; 37,76</t>
+          <t>23,46; 38,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 25,75</t>
+          <t>13,52; 25,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,05; 26,45</t>
+          <t>14,0; 26,33</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,88; 47,63</t>
+          <t>30,81; 47,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,66; 39,89</t>
+          <t>24,67; 39,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,39; 33,62</t>
+          <t>17,05; 32,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,25; 58,13</t>
+          <t>8,18; 61,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,66; 76,13</t>
+          <t>16,54; 77,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,87; 41,4</t>
+          <t>7,88; 39,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,44; 46,96</t>
+          <t>29,83; 45,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,88; 40,63</t>
+          <t>24,8; 40,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,3; 31,18</t>
+          <t>17,27; 31,01</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,52; 52,47</t>
+          <t>33,13; 51,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,98; 46,63</t>
+          <t>29,83; 46,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,49; 35,68</t>
+          <t>20,42; 36,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,33; 83,66</t>
+          <t>0,0; 83,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,26</t>
+          <t>0,0; 63,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,8; 52,04</t>
+          <t>34,04; 51,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,46; 46,37</t>
+          <t>29,57; 45,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,54; 35,2</t>
+          <t>20,55; 35,98</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,46; 30,66</t>
+          <t>23,79; 30,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,9; 22,57</t>
+          <t>16,95; 22,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,13; 22,83</t>
+          <t>16,24; 23,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,31</t>
+          <t>5,14; 12,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,19</t>
+          <t>6,25; 12,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,48</t>
+          <t>6,17; 12,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,99; 24,54</t>
+          <t>19,02; 24,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,96; 18,48</t>
+          <t>14,13; 18,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 18,38</t>
+          <t>13,44; 18,12</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, el consejo médico (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1871</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5347</t>
+          <t>0; 5615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5987</t>
+          <t>0; 5994</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>994; 8434</t>
+          <t>968; 8487</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5486</t>
+          <t>0; 5657</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5910</t>
+          <t>0; 6256</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1000; 8739</t>
+          <t>945; 8589</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1064; 10188</t>
+          <t>1527; 10565</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>964; 9641</t>
+          <t>974; 9829</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1018; 8161</t>
+          <t>1026; 8459</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2103; 12153</t>
+          <t>2007; 12223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2693; 11462</t>
+          <t>2053; 12213</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6841</t>
+          <t>0; 6200</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5071; 18258</t>
+          <t>4722; 17585</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4973; 17652</t>
+          <t>5067; 17876</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1929; 11191</t>
+          <t>1913; 11239</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2168; 13173</t>
+          <t>2138; 13297</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3172; 13450</t>
+          <t>2947; 13707</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>887; 8098</t>
+          <t>897; 8725</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 8299</t>
+          <t>0; 9685</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>956; 7975</t>
+          <t>959; 7910</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>903; 7753</t>
+          <t>916; 8026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3641; 16038</t>
+          <t>3675; 16409</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5695; 18725</t>
+          <t>5077; 18165</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2084; 12452</t>
+          <t>2813; 12496</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13415; 30425</t>
+          <t>13452; 30340</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9366; 25085</t>
+          <t>8879; 24001</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14222; 30898</t>
+          <t>14588; 32668</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6210</t>
+          <t>0; 6270</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4198; 16034</t>
+          <t>4200; 15518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4063; 15191</t>
+          <t>3922; 14779</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14928; 33991</t>
+          <t>14635; 32412</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15904; 34904</t>
+          <t>15454; 34193</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19854; 40761</t>
+          <t>20650; 42074</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33475; 53725</t>
+          <t>32656; 53309</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19454; 40197</t>
+          <t>18844; 38763</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19607; 39159</t>
+          <t>19653; 39789</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4071</t>
+          <t>0; 4965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4677; 15875</t>
+          <t>4215; 16682</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3412; 15282</t>
+          <t>3450; 15046</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33295; 54970</t>
+          <t>34156; 56077</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26436; 49448</t>
+          <t>25965; 49414</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26674; 50234</t>
+          <t>26583; 50009</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37643; 58067</t>
+          <t>37554; 58201</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40082; 64832</t>
+          <t>40100; 63963</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21434; 41425</t>
+          <t>21013; 40415</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1117; 7872</t>
+          <t>1108; 8291</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1132; 8087</t>
+          <t>1757; 8222</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2027; 10665</t>
+          <t>2031; 10129</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41227; 63605</t>
+          <t>40406; 62205</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44812; 70350</t>
+          <t>42951; 70803</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25778; 46452</t>
+          <t>25723; 46203</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37983; 59445</t>
+          <t>37538; 58296</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42419; 65965</t>
+          <t>42199; 66188</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22278; 38796</t>
+          <t>22200; 40120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1046; 7726</t>
+          <t>0; 7707</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4246</t>
+          <t>0; 4064</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 1420</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41421; 63764</t>
+          <t>41715; 63205</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43563; 68580</t>
+          <t>43736; 67765</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21728; 39154</t>
+          <t>22853; 40022</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>146547; 191499</t>
+          <t>148595; 191333</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>137926; 184183</t>
+          <t>138297; 185369</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97643; 138260</t>
+          <t>98347; 139481</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13395; 33379</t>
+          <t>12894; 30914</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24372; 47132</t>
+          <t>24164; 47385</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21270; 41895</t>
+          <t>20725; 41942</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>166235; 214789</t>
+          <t>166517; 214680</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>167872; 222191</t>
+          <t>169939; 222787</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>125999; 173037</t>
+          <t>126555; 170583</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$medico-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$medico-Edad-trans_dic.xlsx
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,36</t>
+          <t>0,0; 39,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,17</t>
+          <t>0,0; 32,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 51,44</t>
+          <t>5,79; 46,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,16</t>
+          <t>0,0; 21,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,37</t>
+          <t>0,0; 18,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 33,1</t>
+          <t>3,63; 30,74</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 26,78</t>
+          <t>2,69; 24,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 13,51</t>
+          <t>1,34; 13,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 17,41</t>
+          <t>2,1; 18,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 17,44</t>
+          <t>3,03; 17,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,74</t>
+          <t>2,66; 14,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,7</t>
+          <t>0,0; 11,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 16,06</t>
+          <t>5,08; 17,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 11,49</t>
+          <t>3,19; 11,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,55</t>
+          <t>1,82; 10,92</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 15,65</t>
+          <t>2,56; 16,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 12,2</t>
+          <t>2,72; 12,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,74</t>
+          <t>1,2; 10,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,62</t>
+          <t>0,0; 12,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,37</t>
+          <t>0,77; 6,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,13</t>
+          <t>1,05; 8,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,85</t>
+          <t>2,38; 10,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,68</t>
+          <t>2,17; 7,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,7</t>
+          <t>1,3; 7,85</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 24,17</t>
+          <t>10,45; 24,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 14,12</t>
+          <t>5,49; 14,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,48; 30,2</t>
+          <t>13,26; 30,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,67</t>
+          <t>0,0; 10,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 16,94</t>
+          <t>4,62; 17,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 16,75</t>
+          <t>4,64; 16,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 17,59</t>
+          <t>8,17; 17,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 13,07</t>
+          <t>6,03; 13,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 21,42</t>
+          <t>10,72; 20,72</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,49; 41,61</t>
+          <t>25,49; 42,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,44; 27,64</t>
+          <t>14,04; 27,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,78; 29,92</t>
+          <t>14,66; 29,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,47</t>
+          <t>0,0; 23,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 32,23</t>
+          <t>8,12; 31,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 26,43</t>
+          <t>5,89; 26,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,46; 38,52</t>
+          <t>23,03; 38,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,52; 25,74</t>
+          <t>13,52; 25,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,0; 26,33</t>
+          <t>13,51; 24,83</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,81; 47,74</t>
+          <t>30,12; 47,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,67; 39,35</t>
+          <t>24,37; 39,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,05; 32,8</t>
+          <t>16,95; 32,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,18; 61,22</t>
+          <t>7,14; 57,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,54; 77,39</t>
+          <t>10,48; 75,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,88; 39,32</t>
+          <t>7,67; 37,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,83; 45,93</t>
+          <t>30,54; 46,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,8; 40,89</t>
+          <t>25,47; 40,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,27; 31,01</t>
+          <t>17,15; 31,4</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1338,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,13; 51,45</t>
+          <t>34,45; 52,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,83; 46,78</t>
+          <t>29,68; 47,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,42; 36,9</t>
+          <t>20,7; 36,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,46</t>
+          <t>11,46; 76,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,42</t>
+          <t>0,0; 65,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,04; 51,58</t>
+          <t>33,32; 51,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,57; 45,82</t>
+          <t>29,7; 46,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,55; 35,98</t>
+          <t>20,7; 36,11</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,79; 30,63</t>
+          <t>23,81; 30,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,95; 22,71</t>
+          <t>16,94; 22,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,24; 23,04</t>
+          <t>16,32; 22,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,33</t>
+          <t>5,37; 12,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,26</t>
+          <t>6,2; 12,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,17; 12,49</t>
+          <t>6,25; 12,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,02; 24,53</t>
+          <t>19,03; 24,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,13; 18,52</t>
+          <t>14,09; 18,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,44; 18,12</t>
+          <t>13,34; 18,32</t>
         </is>
       </c>
     </row>
@@ -1765,32 +1765,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5615</t>
+          <t>0; 6065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5994</t>
+          <t>0; 6182</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>968; 8487</t>
+          <t>956; 7716</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5657</t>
+          <t>0; 5785</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6256</t>
+          <t>0; 6568</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>945; 8589</t>
+          <t>942; 7976</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1527; 10565</t>
+          <t>1062; 9849</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>974; 9829</t>
+          <t>973; 9673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1026; 8459</t>
+          <t>1019; 8806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2007; 12223</t>
+          <t>2122; 12103</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2053; 12213</t>
+          <t>2207; 12215</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6200</t>
+          <t>0; 6671</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4722; 17585</t>
+          <t>5563; 18888</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5067; 17876</t>
+          <t>4958; 17948</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1913; 11239</t>
+          <t>1935; 11638</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2138; 13297</t>
+          <t>2177; 13902</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2947; 13707</t>
+          <t>3051; 13714</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>897; 8725</t>
+          <t>894; 8162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 9685</t>
+          <t>0; 8349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>959; 7910</t>
+          <t>950; 8579</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>916; 8026</t>
+          <t>920; 7529</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3675; 16409</t>
+          <t>3596; 16068</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5077; 18165</t>
+          <t>5131; 17767</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2813; 12496</t>
+          <t>2108; 12740</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13452; 30340</t>
+          <t>13116; 31023</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8879; 24001</t>
+          <t>9321; 24261</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14588; 32668</t>
+          <t>14350; 32461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6270</t>
+          <t>0; 6265</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4200; 15518</t>
+          <t>4231; 15623</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3922; 14779</t>
+          <t>4093; 14747</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14635; 32412</t>
+          <t>15049; 32994</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15454; 34193</t>
+          <t>15778; 35878</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20650; 42074</t>
+          <t>21061; 40689</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32656; 53309</t>
+          <t>32662; 54234</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18844; 38763</t>
+          <t>19684; 39047</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19653; 39789</t>
+          <t>19502; 39111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4965</t>
+          <t>0; 4036</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4215; 16682</t>
+          <t>4202; 16329</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3450; 15046</t>
+          <t>3352; 15203</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34156; 56077</t>
+          <t>33520; 56242</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25965; 49414</t>
+          <t>25963; 49182</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26583; 50009</t>
+          <t>25656; 47158</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37554; 58201</t>
+          <t>36717; 57964</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40100; 63963</t>
+          <t>39610; 64416</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21013; 40415</t>
+          <t>20889; 39824</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1108; 8291</t>
+          <t>966; 7790</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1757; 8222</t>
+          <t>1114; 8019</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2031; 10129</t>
+          <t>1976; 9643</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40406; 62205</t>
+          <t>41366; 62335</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42951; 70803</t>
+          <t>44105; 69948</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25723; 46203</t>
+          <t>25544; 46787</t>
         </is>
       </c>
     </row>
@@ -2728,27 +2728,27 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37538; 58296</t>
+          <t>39032; 59504</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42199; 66188</t>
+          <t>41993; 67492</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22200; 40120</t>
+          <t>22503; 39796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7707</t>
+          <t>1058; 7033</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4064</t>
+          <t>0; 4182</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41715; 63205</t>
+          <t>40829; 63092</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43736; 67765</t>
+          <t>43926; 68641</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22853; 40022</t>
+          <t>23021; 40159</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>148595; 191333</t>
+          <t>148718; 190845</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>138297; 185369</t>
+          <t>138274; 185072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>98347; 139481</t>
+          <t>98799; 136657</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12894; 30914</t>
+          <t>13457; 31506</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24164; 47385</t>
+          <t>23978; 46866</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20725; 41942</t>
+          <t>20976; 41737</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>166517; 214680</t>
+          <t>166531; 214916</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>169939; 222787</t>
+          <t>169436; 221388</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>126555; 170583</t>
+          <t>125552; 172434</t>
         </is>
       </c>
     </row>
